--- a/Word-pair stimulus/Word-lists.xlsx
+++ b/Word-pair stimulus/Word-lists.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\FACTORY\Studio07_York\Manuscript\Repository\Word-pair stimulus\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F02CD57B-DC0B-498F-9CB0-51ECFCE0E555}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{197C3B13-9AA5-4E1B-99B9-919EA73CFF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="2" r:id="rId1"/>
@@ -35,45 +35,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="516">
   <si>
     <t>ID</t>
   </si>
   <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>Dist1</t>
-  </si>
-  <si>
-    <t>Dist2</t>
-  </si>
-  <si>
     <t>List</t>
   </si>
   <si>
     <t>RT</t>
-  </si>
-  <si>
-    <t>Distance_cue_tar</t>
-  </si>
-  <si>
-    <t>Strength_cue</t>
-  </si>
-  <si>
-    <t>Strength_target</t>
-  </si>
-  <si>
-    <t>Concrete_cue</t>
-  </si>
-  <si>
-    <t>Concrete_target</t>
-  </si>
-  <si>
-    <t>Count_cue</t>
-  </si>
-  <si>
-    <t>Count_target</t>
   </si>
   <si>
     <t>apple</t>
@@ -1548,10 +1518,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Cue</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>The average semantic relatedness of the probe word.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1576,18 +1542,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Distance_cue_tar</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Distance_cue_dist1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Distance_cue_dist2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>The semantic distance (based on ConceptNet Numberbatch) between the probe and distractor word 1.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -1596,19 +1550,71 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>Distance_target_dist1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Distance_target_dist2</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>The semantic distance (based on ConceptNet Numberbatch) between the target and distractor word 1.</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>The semantic distance (based on ConceptNet Numberbatch) between the target and distractor word 2.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dist_pro_tar</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dist_pro_dist1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dist_pro_dist2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dist_tar_dist1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dist_tar_dist2</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strength_target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>concrete_target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>count_target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>strength_pro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>soncrete_pro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>count_pro</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>target</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>probe</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dist1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dist2</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -2169,16 +2175,12 @@
     <col min="3" max="4" width="10.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="4.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="18.5" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.25" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.375" customWidth="1"/>
-    <col min="18" max="18" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="13" width="13.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.75" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" ht="14.25" x14ac:dyDescent="0.15">
@@ -2186,55 +2188,55 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
+        <v>513</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H1" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="R1" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:18" ht="14.25" x14ac:dyDescent="0.15">
@@ -2242,19 +2244,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D2" s="6" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F2" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G2" s="2">
         <v>1.8933702564235999</v>
@@ -2298,19 +2300,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G3" s="2">
         <v>2.2471672153475999</v>
@@ -2354,19 +2356,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G4" s="2">
         <v>2.4831727409368001</v>
@@ -2410,19 +2412,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G5" s="2">
         <v>1.9311717987071999</v>
@@ -2466,19 +2468,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G6" s="2">
         <v>2.0392140483868002</v>
@@ -2522,19 +2524,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2">
         <v>1.7922048759460001</v>
@@ -2578,19 +2580,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2">
         <v>1.8460463428492</v>
@@ -2634,19 +2636,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G9" s="2">
         <v>2.0156825637816</v>
@@ -2690,19 +2692,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G10" s="2">
         <v>2.2652525901792</v>
@@ -2746,19 +2748,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G11" s="2">
         <v>1.6287994480136001</v>
@@ -2802,19 +2804,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G12" s="2">
         <v>1.92649876594548</v>
@@ -2858,19 +2860,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G13" s="2">
         <v>1.9109057521813599</v>
@@ -2914,19 +2916,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G14" s="2">
         <v>1.8873249912256</v>
@@ -2970,19 +2972,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G15" s="2">
         <v>2.1978433990480002</v>
@@ -3026,19 +3028,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G16" s="2">
         <v>2.1165219688415999</v>
@@ -3082,19 +3084,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G17" s="2">
         <v>1.6878831958767999</v>
@@ -3138,19 +3140,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G18" s="2">
         <v>2.082305641174</v>
@@ -3194,19 +3196,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G19" s="2">
         <v>2.0757709884644</v>
@@ -3250,19 +3252,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G20" s="2">
         <v>1.7517756366725199</v>
@@ -3306,19 +3308,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G21" s="2">
         <v>1.8411270332341201</v>
@@ -3362,19 +3364,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G22" s="2">
         <v>1.5646401691444001</v>
@@ -3418,19 +3420,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G23" s="2">
         <v>2.3336133575444</v>
@@ -3474,19 +3476,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="D24" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E24" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="6" t="s">
-        <v>96</v>
-      </c>
       <c r="F24" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G24" s="2">
         <v>1.9290748786936001</v>
@@ -3530,19 +3532,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G25" s="2">
         <v>2.4580431461332002</v>
@@ -3586,19 +3588,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G26" s="2">
         <v>1.9538271903990001</v>
@@ -3642,19 +3644,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="E27" s="6" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G27" s="2">
         <v>2.5984466075900001</v>
@@ -3698,19 +3700,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="5" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G28" s="2">
         <v>2.4679236888888001</v>
@@ -3754,19 +3756,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="5" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="E29" s="6" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G29" s="2">
         <v>1.9634031009684001</v>
@@ -3810,19 +3812,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="5" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="E30" s="6" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G30" s="2">
         <v>2.0694533348083999</v>
@@ -3866,19 +3868,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G31" s="2">
         <v>1.6520769786831999</v>
@@ -3922,19 +3924,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E32" s="6" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G32" s="2">
         <v>2.3121567153935998</v>
@@ -3978,19 +3980,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="5" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="E33" s="6" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G33" s="2">
         <v>1.9504049682619999</v>
@@ -4034,19 +4036,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="5" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="E34" s="6" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G34" s="2">
         <v>2.7091396236428</v>
@@ -4090,19 +4092,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G35" s="2">
         <v>1.7426415634143599</v>
@@ -4146,19 +4148,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E36" s="6" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G36" s="2">
         <v>1.5668990612022</v>
@@ -4202,19 +4204,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G37" s="2">
         <v>1.9013150024415999</v>
@@ -4258,19 +4260,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G38" s="2">
         <v>2.0816215610508002</v>
@@ -4314,19 +4316,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G39" s="2">
         <v>2.1461610126488</v>
@@ -4370,19 +4372,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G40" s="2">
         <v>2.0663685321815999</v>
@@ -4426,19 +4428,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="E41" s="6" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G41" s="2">
         <v>1.93615997314424</v>
@@ -4482,19 +4484,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G42" s="2">
         <v>1.6949220466612001</v>
@@ -4536,19 +4538,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>155</v>
+        <v>145</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="E43" s="6" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G43" s="2">
         <v>1.49472409248344</v>
@@ -4592,19 +4594,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="5" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="E44" s="6" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G44" s="2">
         <v>1.50537381172272</v>
@@ -4648,19 +4650,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="5" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G45" s="2">
         <v>1.3843668460845999</v>
@@ -4704,19 +4706,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="5" t="s">
-        <v>167</v>
+        <v>157</v>
       </c>
       <c r="C46" s="6" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="D46" s="6" t="s">
-        <v>169</v>
+        <v>159</v>
       </c>
       <c r="E46" s="6" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G46" s="2">
         <v>1.7001383876808001</v>
@@ -4760,19 +4762,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="5" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C47" s="6" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="D47" s="6" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="E47" s="6" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G47" s="2">
         <v>1.92032142639216</v>
@@ -4816,19 +4818,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="5" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C48" s="6" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D48" s="6" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="E48" s="6" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G48" s="2">
         <v>1.43117188453704</v>
@@ -4872,19 +4874,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="5" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D49" s="6" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G49" s="2">
         <v>1.6407911205287999</v>
@@ -4928,19 +4930,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="5" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="C50" s="6" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="D50" s="6" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="E50" s="6" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G50" s="2">
         <v>1.2862990951538</v>
@@ -4984,19 +4986,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="C51" s="6" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D51" s="6" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="E51" s="6" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G51" s="2">
         <v>1.7251818275444</v>
@@ -5040,19 +5042,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="5" t="s">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D52" s="6" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G52" s="2">
         <v>1.3681953334807599</v>
@@ -5096,19 +5098,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="5" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="C53" s="6" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="D53" s="6" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="E53" s="6" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G53" s="2">
         <v>1.6898830795290001</v>
@@ -5152,19 +5154,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="5" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C54" s="6" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D54" s="6" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="E54" s="6" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G54" s="2">
         <v>1.69333422660772</v>
@@ -5208,19 +5210,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G55" s="2">
         <v>1.7270034313198399</v>
@@ -5264,19 +5266,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="5" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G56" s="2">
         <v>2.1431525039675998</v>
@@ -5320,19 +5322,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="5" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G57" s="2">
         <v>1.76756680488548</v>
@@ -5376,19 +5378,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="E58" s="6" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G58" s="2">
         <v>1.4420253276830399</v>
@@ -5432,19 +5434,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="5" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G59" s="2">
         <v>1.5015892696390001</v>
@@ -5488,19 +5490,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="5" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="C60" s="6" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="E60" s="6" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G60" s="2">
         <v>1.6202924060828401</v>
@@ -5544,19 +5546,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="5" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G61" s="2">
         <v>1.9660409927356</v>
@@ -5600,19 +5602,19 @@
         <v>61</v>
       </c>
       <c r="B62" s="5" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="C62" s="6" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="E62" s="6" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G62" s="2">
         <v>1.7253479576105999</v>
@@ -5656,19 +5658,19 @@
         <v>62</v>
       </c>
       <c r="B63" s="5" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G63" s="2">
         <v>1.8143371677408</v>
@@ -5712,19 +5714,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="5" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="C64" s="6" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="E64" s="6" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G64" s="2">
         <v>1.5599322319038</v>
@@ -5768,19 +5770,19 @@
         <v>64</v>
       </c>
       <c r="B65" s="5" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="C65" s="6" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="D65" s="6" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="E65" s="6" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G65" s="2">
         <v>1.61985198974704</v>
@@ -5824,19 +5826,19 @@
         <v>65</v>
       </c>
       <c r="B66" s="5" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="C66" s="6" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="D66" s="6" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="E66" s="6" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G66" s="2">
         <v>1.5440817546840799</v>
@@ -5878,19 +5880,19 @@
         <v>66</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="C67" s="6" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="D67" s="6" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="E67" s="6" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G67" s="2">
         <v>1.8374323558811601</v>
@@ -5934,19 +5936,19 @@
         <v>67</v>
       </c>
       <c r="B68" s="5" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="C68" s="6" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="D68" s="6" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="E68" s="6" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G68" s="2">
         <v>1.5026382350919201</v>
@@ -5990,19 +5992,19 @@
         <v>68</v>
       </c>
       <c r="B69" s="5" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C69" s="6" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="E69" s="6" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G69" s="2">
         <v>1.2697701263430401</v>
@@ -6046,19 +6048,19 @@
         <v>69</v>
       </c>
       <c r="B70" s="5" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="C70" s="6" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="D70" s="6" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="E70" s="6" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G70" s="2">
         <v>1.8179466629029599</v>
@@ -6102,19 +6104,19 @@
         <v>70</v>
       </c>
       <c r="B71" s="5" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="C71" s="6" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="E71" s="6" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G71" s="2">
         <v>1.6659189128874401</v>
@@ -6156,19 +6158,19 @@
         <v>71</v>
       </c>
       <c r="B72" s="5" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="C72" s="6" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="E72" s="6" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G72" s="2">
         <v>1.61949754714936</v>
@@ -6212,19 +6214,19 @@
         <v>72</v>
       </c>
       <c r="B73" s="5" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="C73" s="6" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="E73" s="6" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G73" s="2">
         <v>1.6829650306700801</v>
@@ -6268,19 +6270,19 @@
         <v>73</v>
       </c>
       <c r="B74" s="5" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="C74" s="6" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="E74" s="6" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G74" s="2">
         <v>1.7911705684671999</v>
@@ -6324,19 +6326,19 @@
         <v>74</v>
       </c>
       <c r="B75" s="5" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="E75" s="6" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G75" s="2">
         <v>1.56661572456372</v>
@@ -6380,19 +6382,19 @@
         <v>75</v>
       </c>
       <c r="B76" s="5" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="C76" s="6" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="E76" s="6" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G76" s="2">
         <v>1.6035116481782401</v>
@@ -6436,19 +6438,19 @@
         <v>76</v>
       </c>
       <c r="B77" s="5" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="C77" s="6" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D77" s="6" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="E77" s="6" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G77" s="2">
         <v>1.5946801662434</v>
@@ -6492,19 +6494,19 @@
         <v>77</v>
       </c>
       <c r="B78" s="5" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="C78" s="6" t="s">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D78" s="6" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="E78" s="6" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G78" s="2">
         <v>1.5048992252348401</v>
@@ -6548,19 +6550,19 @@
         <v>78</v>
       </c>
       <c r="B79" s="5" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="C79" s="6" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="D79" s="6" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="E79" s="6" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G79" s="2">
         <v>1.6991308212276399</v>
@@ -6604,19 +6606,19 @@
         <v>79</v>
       </c>
       <c r="B80" s="5" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="C80" s="6" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D80" s="6" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="E80" s="6" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="F80" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G80" s="2">
         <v>1.6431490516659999</v>
@@ -6660,19 +6662,19 @@
         <v>80</v>
       </c>
       <c r="B81" s="5" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="E81" s="6" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="F81" s="6" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="G81" s="2">
         <v>1.52588545799256</v>
@@ -6716,19 +6718,19 @@
         <v>81</v>
       </c>
       <c r="B82" s="5" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="C82" s="6" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="E82" s="6" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G82" s="2">
         <v>2.3427112897242899</v>
@@ -6772,19 +6774,19 @@
         <v>82</v>
       </c>
       <c r="B83" s="5" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="C83" s="6" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="D83" s="6" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="E83" s="6" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="F83" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G83" s="2">
         <v>1.94758055323705</v>
@@ -6828,19 +6830,19 @@
         <v>83</v>
       </c>
       <c r="B84" s="5" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="C84" s="6" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="D84" s="6" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="E84" s="6" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G84" s="2">
         <v>2.0337635903132898</v>
@@ -6884,19 +6886,19 @@
         <v>84</v>
       </c>
       <c r="B85" s="5" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G85" s="2">
         <v>1.7978678544361899</v>
@@ -6940,19 +6942,19 @@
         <v>85</v>
       </c>
       <c r="B86" s="5" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="C86" s="6" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="E86" s="6" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G86" s="2">
         <v>2.5249665010547599</v>
@@ -6996,19 +6998,19 @@
         <v>86</v>
       </c>
       <c r="B87" s="5" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G87" s="2">
         <v>1.79753109386948</v>
@@ -7052,19 +7054,19 @@
         <v>87</v>
       </c>
       <c r="B88" s="5" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="C88" s="6" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D88" s="6" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="E88" s="6" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="F88" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G88" s="2">
         <v>1.8017510913652399</v>
@@ -7108,19 +7110,19 @@
         <v>88</v>
       </c>
       <c r="B89" s="5" t="s">
-        <v>312</v>
+        <v>302</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>313</v>
+        <v>303</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="E89" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="F89" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="F89" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="G89" s="2">
         <v>1.6576387768697101</v>
@@ -7164,19 +7166,19 @@
         <v>89</v>
       </c>
       <c r="B90" s="5" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="C90" s="6" t="s">
-        <v>315</v>
+        <v>305</v>
       </c>
       <c r="D90" s="6" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="E90" s="6" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="F90" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G90" s="2">
         <v>1.64116710708333</v>
@@ -7220,19 +7222,19 @@
         <v>90</v>
       </c>
       <c r="B91" s="5" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>319</v>
+        <v>309</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G91" s="2">
         <v>1.9822565941581001</v>
@@ -7276,19 +7278,19 @@
         <v>91</v>
       </c>
       <c r="B92" s="5" t="s">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="C92" s="6" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D92" s="6" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G92" s="2">
         <v>1.92934700421095</v>
@@ -7332,19 +7334,19 @@
         <v>92</v>
       </c>
       <c r="B93" s="5" t="s">
-        <v>322</v>
+        <v>312</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>323</v>
+        <v>313</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G93" s="2">
         <v>1.8918849286583299</v>
@@ -7388,19 +7390,19 @@
         <v>93</v>
       </c>
       <c r="B94" s="5" t="s">
-        <v>325</v>
+        <v>315</v>
       </c>
       <c r="C94" s="6" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="D94" s="6" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="E94" s="6" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="F94" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G94" s="2">
         <v>2.0731869198023798</v>
@@ -7444,19 +7446,19 @@
         <v>94</v>
       </c>
       <c r="B95" s="5" t="s">
-        <v>326</v>
+        <v>316</v>
       </c>
       <c r="C95" s="6" t="s">
-        <v>327</v>
+        <v>317</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>328</v>
+        <v>318</v>
       </c>
       <c r="E95" s="6" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="F95" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G95" s="2">
         <v>2.5475357260023799</v>
@@ -7500,19 +7502,19 @@
         <v>95</v>
       </c>
       <c r="B96" s="5" t="s">
-        <v>329</v>
+        <v>319</v>
       </c>
       <c r="C96" s="6" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>331</v>
+        <v>321</v>
       </c>
       <c r="E96" s="6" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="F96" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G96" s="2">
         <v>2.4103981426785701</v>
@@ -7556,19 +7558,19 @@
         <v>96</v>
       </c>
       <c r="B97" s="5" t="s">
-        <v>332</v>
+        <v>322</v>
       </c>
       <c r="C97" s="6" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="D97" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="E97" s="6" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="F97" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G97" s="2">
         <v>2.17111437661314</v>
@@ -7612,19 +7614,19 @@
         <v>97</v>
       </c>
       <c r="B98" s="5" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="C98" s="6" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="E98" s="6" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="F98" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G98" s="2">
         <v>2.2132454826714301</v>
@@ -7668,19 +7670,19 @@
         <v>98</v>
       </c>
       <c r="B99" s="5" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="C99" s="6" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="D99" s="6" t="s">
-        <v>339</v>
+        <v>329</v>
       </c>
       <c r="E99" s="6" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="F99" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G99" s="2">
         <v>1.9257215658819999</v>
@@ -7724,19 +7726,19 @@
         <v>99</v>
       </c>
       <c r="B100" s="5" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="C100" s="6" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="D100" s="6" t="s">
-        <v>342</v>
+        <v>332</v>
       </c>
       <c r="E100" s="6" t="s">
-        <v>343</v>
+        <v>333</v>
       </c>
       <c r="F100" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G100" s="2">
         <v>2.7236718677338101</v>
@@ -7780,19 +7782,19 @@
         <v>100</v>
       </c>
       <c r="B101" s="5" t="s">
-        <v>344</v>
+        <v>334</v>
       </c>
       <c r="C101" s="6" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="D101" s="6" t="s">
-        <v>321</v>
+        <v>311</v>
       </c>
       <c r="E101" s="6" t="s">
-        <v>314</v>
+        <v>304</v>
       </c>
       <c r="F101" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G101" s="2">
         <v>2.06244812692852</v>
@@ -7836,19 +7838,19 @@
         <v>101</v>
       </c>
       <c r="B102" s="5" t="s">
-        <v>346</v>
+        <v>336</v>
       </c>
       <c r="C102" s="6" t="s">
-        <v>347</v>
+        <v>337</v>
       </c>
       <c r="D102" s="6" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E102" s="6" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="F102" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G102" s="2">
         <v>1.87017700785714</v>
@@ -7892,19 +7894,19 @@
         <v>102</v>
       </c>
       <c r="B103" s="5" t="s">
-        <v>348</v>
+        <v>338</v>
       </c>
       <c r="C103" s="6" t="s">
-        <v>349</v>
+        <v>339</v>
       </c>
       <c r="D103" s="6" t="s">
-        <v>350</v>
+        <v>340</v>
       </c>
       <c r="E103" s="6" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="F103" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G103" s="2">
         <v>1.77093633015895</v>
@@ -7948,19 +7950,19 @@
         <v>103</v>
       </c>
       <c r="B104" s="5" t="s">
-        <v>352</v>
+        <v>342</v>
       </c>
       <c r="C104" s="6" t="s">
-        <v>353</v>
+        <v>343</v>
       </c>
       <c r="D104" s="6" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="E104" s="6" t="s">
-        <v>355</v>
+        <v>345</v>
       </c>
       <c r="F104" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G104" s="2">
         <v>1.8320340088438101</v>
@@ -8004,19 +8006,19 @@
         <v>104</v>
       </c>
       <c r="B105" s="5" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C105" s="6" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="E105" s="6" t="s">
-        <v>354</v>
+        <v>344</v>
       </c>
       <c r="F105" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G105" s="2">
         <v>2.4758423850647602</v>
@@ -8060,19 +8062,19 @@
         <v>105</v>
       </c>
       <c r="B106" s="5" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="C106" s="6" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D106" s="6" t="s">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="E106" s="6" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="F106" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G106" s="2">
         <v>3.0394882588157102</v>
@@ -8116,19 +8118,19 @@
         <v>106</v>
       </c>
       <c r="B107" s="5" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="C107" s="6" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="D107" s="6" t="s">
-        <v>363</v>
+        <v>353</v>
       </c>
       <c r="E107" s="6" t="s">
-        <v>364</v>
+        <v>354</v>
       </c>
       <c r="F107" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G107" s="2">
         <v>1.9099431605567601</v>
@@ -8172,19 +8174,19 @@
         <v>107</v>
       </c>
       <c r="B108" s="5" t="s">
-        <v>365</v>
+        <v>355</v>
       </c>
       <c r="C108" s="6" t="s">
-        <v>366</v>
+        <v>356</v>
       </c>
       <c r="D108" s="6" t="s">
-        <v>367</v>
+        <v>357</v>
       </c>
       <c r="E108" s="6" t="s">
-        <v>368</v>
+        <v>358</v>
       </c>
       <c r="F108" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G108" s="2">
         <v>1.9985709530971401</v>
@@ -8228,19 +8230,19 @@
         <v>108</v>
       </c>
       <c r="B109" s="5" t="s">
-        <v>369</v>
+        <v>359</v>
       </c>
       <c r="C109" s="6" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="D109" s="6" t="s">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="E109" s="6" t="s">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F109" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G109" s="2">
         <v>2.3775902362100001</v>
@@ -8284,19 +8286,19 @@
         <v>109</v>
       </c>
       <c r="B110" s="5" t="s">
-        <v>371</v>
+        <v>361</v>
       </c>
       <c r="C110" s="6" t="s">
-        <v>372</v>
+        <v>362</v>
       </c>
       <c r="D110" s="6" t="s">
-        <v>373</v>
+        <v>363</v>
       </c>
       <c r="E110" s="6" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="F110" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G110" s="2">
         <v>1.8010225977208101</v>
@@ -8340,19 +8342,19 @@
         <v>110</v>
       </c>
       <c r="B111" s="5" t="s">
-        <v>374</v>
+        <v>364</v>
       </c>
       <c r="C111" s="6" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="D111" s="6" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="E111" s="6" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="F111" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G111" s="2">
         <v>2.1836175123857098</v>
@@ -8396,19 +8398,19 @@
         <v>111</v>
       </c>
       <c r="B112" s="5" t="s">
-        <v>377</v>
+        <v>367</v>
       </c>
       <c r="C112" s="6" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D112" s="6" t="s">
-        <v>378</v>
+        <v>368</v>
       </c>
       <c r="E112" s="6" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="F112" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G112" s="2">
         <v>1.59996573130333</v>
@@ -8452,19 +8454,19 @@
         <v>112</v>
       </c>
       <c r="B113" s="5" t="s">
-        <v>379</v>
+        <v>369</v>
       </c>
       <c r="C113" s="6" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="E113" s="6" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="F113" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G113" s="2">
         <v>1.9403914269943801</v>
@@ -8508,19 +8510,19 @@
         <v>113</v>
       </c>
       <c r="B114" s="5" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="C114" s="6" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="D114" s="6" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E114" s="6" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="F114" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G114" s="2">
         <v>2.2456543899728598</v>
@@ -8564,19 +8566,19 @@
         <v>114</v>
       </c>
       <c r="B115" s="5" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>384</v>
+        <v>374</v>
       </c>
       <c r="F115" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G115" s="2">
         <v>2.1238034793295202</v>
@@ -8620,19 +8622,19 @@
         <v>115</v>
       </c>
       <c r="B116" s="5" t="s">
-        <v>385</v>
+        <v>375</v>
       </c>
       <c r="C116" s="6" t="s">
-        <v>386</v>
+        <v>376</v>
       </c>
       <c r="D116" s="6" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="E116" s="6" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="F116" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G116" s="2">
         <v>2.1180048783619099</v>
@@ -8676,19 +8678,19 @@
         <v>116</v>
       </c>
       <c r="B117" s="5" t="s">
-        <v>388</v>
+        <v>378</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>391</v>
+        <v>381</v>
       </c>
       <c r="F117" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G117" s="2">
         <v>1.6811494940804801</v>
@@ -8732,19 +8734,19 @@
         <v>117</v>
       </c>
       <c r="B118" s="5" t="s">
-        <v>392</v>
+        <v>382</v>
       </c>
       <c r="C118" s="6" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="D118" s="6" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="E118" s="6" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="F118" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G118" s="2">
         <v>1.9086780888695201</v>
@@ -8788,19 +8790,19 @@
         <v>118</v>
       </c>
       <c r="B119" s="5" t="s">
-        <v>393</v>
+        <v>383</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>394</v>
+        <v>384</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>395</v>
+        <v>385</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G119" s="2">
         <v>2.9724541845780998</v>
@@ -8844,19 +8846,19 @@
         <v>119</v>
       </c>
       <c r="B120" s="5" t="s">
-        <v>396</v>
+        <v>386</v>
       </c>
       <c r="C120" s="6" t="s">
-        <v>397</v>
+        <v>387</v>
       </c>
       <c r="D120" s="6" t="s">
-        <v>351</v>
+        <v>341</v>
       </c>
       <c r="E120" s="6" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="F120" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G120" s="2">
         <v>2.4855183760319002</v>
@@ -8900,19 +8902,19 @@
         <v>120</v>
       </c>
       <c r="B121" s="5" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>398</v>
+        <v>388</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>399</v>
+        <v>389</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G121" s="2">
         <v>1.91325180871095</v>
@@ -8956,19 +8958,19 @@
         <v>121</v>
       </c>
       <c r="B122" s="5" t="s">
-        <v>400</v>
+        <v>390</v>
       </c>
       <c r="C122" s="6" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>401</v>
+        <v>391</v>
       </c>
       <c r="E122" s="6" t="s">
-        <v>402</v>
+        <v>392</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G122" s="2">
         <v>1.5659260182155701</v>
@@ -9012,19 +9014,19 @@
         <v>122</v>
       </c>
       <c r="B123" s="5" t="s">
-        <v>403</v>
+        <v>393</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>404</v>
+        <v>394</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G123" s="2">
         <v>2.38692334720057</v>
@@ -9066,19 +9068,19 @@
         <v>123</v>
       </c>
       <c r="B124" s="5" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="C124" s="6" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>406</v>
+        <v>396</v>
       </c>
       <c r="E124" s="6" t="s">
-        <v>407</v>
+        <v>397</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G124" s="2">
         <v>1.7594380605791899</v>
@@ -9122,19 +9124,19 @@
         <v>124</v>
       </c>
       <c r="B125" s="5" t="s">
-        <v>408</v>
+        <v>398</v>
       </c>
       <c r="C125" s="6" t="s">
-        <v>409</v>
+        <v>399</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>410</v>
+        <v>400</v>
       </c>
       <c r="E125" s="6" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G125" s="2">
         <v>1.4320040203270501</v>
@@ -9178,19 +9180,19 @@
         <v>125</v>
       </c>
       <c r="B126" s="5" t="s">
-        <v>387</v>
+        <v>377</v>
       </c>
       <c r="C126" s="6" t="s">
-        <v>411</v>
+        <v>401</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>412</v>
+        <v>402</v>
       </c>
       <c r="E126" s="6" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G126" s="2">
         <v>1.7367725372303799</v>
@@ -9234,19 +9236,19 @@
         <v>126</v>
       </c>
       <c r="B127" s="5" t="s">
-        <v>413</v>
+        <v>403</v>
       </c>
       <c r="C127" s="6" t="s">
-        <v>324</v>
+        <v>314</v>
       </c>
       <c r="D127" s="6" t="s">
-        <v>414</v>
+        <v>404</v>
       </c>
       <c r="E127" s="6" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="F127" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G127" s="2">
         <v>1.5343936284384301</v>
@@ -9290,19 +9292,19 @@
         <v>127</v>
       </c>
       <c r="B128" s="5" t="s">
-        <v>415</v>
+        <v>405</v>
       </c>
       <c r="C128" s="6" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D128" s="6" t="s">
-        <v>416</v>
+        <v>406</v>
       </c>
       <c r="E128" s="6" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F128" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G128" s="2">
         <v>2.1083590076091898</v>
@@ -9346,19 +9348,19 @@
         <v>128</v>
       </c>
       <c r="B129" s="5" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="C129" s="6" t="s">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="E129" s="6" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G129" s="2">
         <v>1.6314039911534299</v>
@@ -9402,19 +9404,19 @@
         <v>129</v>
       </c>
       <c r="B130" s="5" t="s">
-        <v>419</v>
+        <v>409</v>
       </c>
       <c r="C130" s="6" t="s">
-        <v>420</v>
+        <v>410</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="E130" s="6" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G130" s="2">
         <v>1.6367609614419101</v>
@@ -9458,19 +9460,19 @@
         <v>130</v>
       </c>
       <c r="B131" s="5" t="s">
-        <v>421</v>
+        <v>411</v>
       </c>
       <c r="C131" s="6" t="s">
-        <v>422</v>
+        <v>412</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>423</v>
+        <v>413</v>
       </c>
       <c r="E131" s="6" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G131" s="2">
         <v>1.51797291210681</v>
@@ -9514,19 +9516,19 @@
         <v>131</v>
       </c>
       <c r="B132" s="5" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="C132" s="6" t="s">
-        <v>376</v>
+        <v>366</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E132" s="6" t="s">
-        <v>375</v>
+        <v>365</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G132" s="2">
         <v>1.7861384323670499</v>
@@ -9570,19 +9572,19 @@
         <v>132</v>
       </c>
       <c r="B133" s="5" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="C133" s="6" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="E133" s="6" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G133" s="2">
         <v>1.85885445277048</v>
@@ -9626,19 +9628,19 @@
         <v>133</v>
       </c>
       <c r="B134" s="5" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="C134" s="6" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>341</v>
+        <v>331</v>
       </c>
       <c r="E134" s="6" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G134" s="2">
         <v>1.6641763278414301</v>
@@ -9682,19 +9684,19 @@
         <v>134</v>
       </c>
       <c r="B135" s="5" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="E135" s="6" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G135" s="2">
         <v>1.51422507422286</v>
@@ -9736,19 +9738,19 @@
         <v>135</v>
       </c>
       <c r="B136" s="5" t="s">
-        <v>58</v>
+        <v>48</v>
       </c>
       <c r="C136" s="6" t="s">
-        <v>333</v>
+        <v>323</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="E136" s="6" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G136" s="2">
         <v>2.0765779018389998</v>
@@ -9790,19 +9792,19 @@
         <v>136</v>
       </c>
       <c r="B137" s="5" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="C137" s="6" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="E137" s="6" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G137" s="2">
         <v>1.6923080512456701</v>
@@ -9846,19 +9848,19 @@
         <v>137</v>
       </c>
       <c r="B138" s="5" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="C138" s="6" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="E138" s="6" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G138" s="2">
         <v>1.59294036456448</v>
@@ -9902,19 +9904,19 @@
         <v>138</v>
       </c>
       <c r="B139" s="5" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="C139" s="6" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="E139" s="6" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G139" s="2">
         <v>1.7142511776515701</v>
@@ -9958,19 +9960,19 @@
         <v>139</v>
       </c>
       <c r="B140" s="5" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="C140" s="6" t="s">
-        <v>154</v>
+        <v>144</v>
       </c>
       <c r="D140" s="6" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="E140" s="6" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F140" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G140" s="2">
         <v>1.61491044362405</v>
@@ -10014,19 +10016,19 @@
         <v>140</v>
       </c>
       <c r="B141" s="5" t="s">
-        <v>446</v>
+        <v>436</v>
       </c>
       <c r="C141" s="6" t="s">
-        <v>447</v>
+        <v>437</v>
       </c>
       <c r="D141" s="6" t="s">
-        <v>448</v>
+        <v>438</v>
       </c>
       <c r="E141" s="6" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="F141" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G141" s="2">
         <v>1.56841473352257</v>
@@ -10070,19 +10072,19 @@
         <v>141</v>
       </c>
       <c r="B142" s="5" t="s">
-        <v>450</v>
+        <v>440</v>
       </c>
       <c r="C142" s="6" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>449</v>
+        <v>439</v>
       </c>
       <c r="E142" s="6" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G142" s="2">
         <v>1.52197803769757</v>
@@ -10126,19 +10128,19 @@
         <v>142</v>
       </c>
       <c r="B143" s="5" t="s">
-        <v>452</v>
+        <v>442</v>
       </c>
       <c r="C143" s="6" t="s">
-        <v>453</v>
+        <v>443</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="E143" s="6" t="s">
-        <v>454</v>
+        <v>444</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G143" s="2">
         <v>1.3985804376159501</v>
@@ -10182,19 +10184,19 @@
         <v>143</v>
       </c>
       <c r="B144" s="5" t="s">
-        <v>455</v>
+        <v>445</v>
       </c>
       <c r="C144" s="6" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>345</v>
+        <v>335</v>
       </c>
       <c r="E144" s="6" t="s">
-        <v>456</v>
+        <v>446</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G144" s="2">
         <v>1.31155892780852</v>
@@ -10236,19 +10238,19 @@
         <v>144</v>
       </c>
       <c r="B145" s="5" t="s">
-        <v>457</v>
+        <v>447</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>458</v>
+        <v>448</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>459</v>
+        <v>449</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>460</v>
+        <v>450</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G145" s="2">
         <v>1.3468186968845199</v>
@@ -10290,19 +10292,19 @@
         <v>145</v>
       </c>
       <c r="B146" s="5" t="s">
-        <v>461</v>
+        <v>451</v>
       </c>
       <c r="C146" s="6" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="D146" s="6" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="E146" s="6" t="s">
-        <v>463</v>
+        <v>453</v>
       </c>
       <c r="F146" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G146" s="2">
         <v>1.68777017366267</v>
@@ -10346,19 +10348,19 @@
         <v>146</v>
       </c>
       <c r="B147" s="5" t="s">
-        <v>464</v>
+        <v>454</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>465</v>
+        <v>455</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>466</v>
+        <v>456</v>
       </c>
       <c r="F147" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G147" s="2">
         <v>1.7818614868887599</v>
@@ -10402,19 +10404,19 @@
         <v>147</v>
       </c>
       <c r="B148" s="5" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="C148" s="6" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E148" s="6" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G148" s="2">
         <v>1.421951577777</v>
@@ -10458,19 +10460,19 @@
         <v>148</v>
       </c>
       <c r="B149" s="5" t="s">
-        <v>467</v>
+        <v>457</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>468</v>
+        <v>458</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E149" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="F149" s="6" t="s">
         <v>280</v>
-      </c>
-      <c r="F149" s="6" t="s">
-        <v>290</v>
       </c>
       <c r="G149" s="2">
         <v>1.4015121232893799</v>
@@ -10514,19 +10516,19 @@
         <v>149</v>
       </c>
       <c r="B150" s="5" t="s">
-        <v>469</v>
+        <v>459</v>
       </c>
       <c r="C150" s="6" t="s">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D150" s="6" t="s">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="E150" s="6" t="s">
-        <v>471</v>
+        <v>461</v>
       </c>
       <c r="F150" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G150" s="2">
         <v>1.4896746135907599</v>
@@ -10570,19 +10572,19 @@
         <v>150</v>
       </c>
       <c r="B151" s="5" t="s">
-        <v>472</v>
+        <v>462</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="F151" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G151" s="2">
         <v>1.63885372025662</v>
@@ -10626,19 +10628,19 @@
         <v>151</v>
       </c>
       <c r="B152" s="5" t="s">
-        <v>473</v>
+        <v>463</v>
       </c>
       <c r="C152" s="6" t="s">
-        <v>474</v>
+        <v>464</v>
       </c>
       <c r="D152" s="6" t="s">
-        <v>475</v>
+        <v>465</v>
       </c>
       <c r="E152" s="6" t="s">
-        <v>476</v>
+        <v>466</v>
       </c>
       <c r="F152" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G152" s="2">
         <v>1.7754779316131899</v>
@@ -10682,19 +10684,19 @@
         <v>152</v>
       </c>
       <c r="B153" s="5" t="s">
-        <v>477</v>
+        <v>467</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>478</v>
+        <v>468</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>479</v>
+        <v>469</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>330</v>
+        <v>320</v>
       </c>
       <c r="F153" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G153" s="2">
         <v>1.4935519922331899</v>
@@ -10736,19 +10738,19 @@
         <v>153</v>
       </c>
       <c r="B154" s="5" t="s">
-        <v>480</v>
+        <v>470</v>
       </c>
       <c r="C154" s="6" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="D154" s="6" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="E154" s="6" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="F154" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G154" s="2">
         <v>1.7136407239090501</v>
@@ -10792,19 +10794,19 @@
         <v>154</v>
       </c>
       <c r="B155" s="5" t="s">
-        <v>451</v>
+        <v>441</v>
       </c>
       <c r="C155" s="6" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="D155" s="6" t="s">
-        <v>462</v>
+        <v>452</v>
       </c>
       <c r="E155" s="6" t="s">
-        <v>482</v>
+        <v>472</v>
       </c>
       <c r="F155" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G155" s="2">
         <v>1.58086328279438</v>
@@ -10848,19 +10850,19 @@
         <v>155</v>
       </c>
       <c r="B156" s="5" t="s">
-        <v>483</v>
+        <v>473</v>
       </c>
       <c r="C156" s="6" t="s">
-        <v>484</v>
+        <v>474</v>
       </c>
       <c r="D156" s="6" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="E156" s="6" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="F156" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G156" s="2">
         <v>2.3621482735581001</v>
@@ -10904,19 +10906,19 @@
         <v>156</v>
       </c>
       <c r="B157" s="5" t="s">
-        <v>485</v>
+        <v>475</v>
       </c>
       <c r="C157" s="6" t="s">
-        <v>486</v>
+        <v>476</v>
       </c>
       <c r="D157" s="6" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="E157" s="6" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="F157" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G157" s="2">
         <v>1.48454381170757</v>
@@ -10960,19 +10962,19 @@
         <v>157</v>
       </c>
       <c r="B158" s="5" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="C158" s="6" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="D158" s="6" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="E158" s="6" t="s">
-        <v>487</v>
+        <v>477</v>
       </c>
       <c r="F158" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G158" s="2">
         <v>1.5576561178484301</v>
@@ -11016,19 +11018,19 @@
         <v>158</v>
       </c>
       <c r="B159" s="5" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="C159" s="6" t="s">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="D159" s="6" t="s">
-        <v>481</v>
+        <v>471</v>
       </c>
       <c r="E159" s="6" t="s">
-        <v>489</v>
+        <v>479</v>
       </c>
       <c r="F159" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G159" s="2">
         <v>1.55729799043571</v>
@@ -11072,19 +11074,19 @@
         <v>159</v>
       </c>
       <c r="B160" s="5" t="s">
-        <v>490</v>
+        <v>480</v>
       </c>
       <c r="C160" s="6" t="s">
-        <v>491</v>
+        <v>481</v>
       </c>
       <c r="D160" s="6" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="E160" s="6" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="F160" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G160" s="2">
         <v>1.62799412863495</v>
@@ -11128,19 +11130,19 @@
         <v>160</v>
       </c>
       <c r="B161" s="5" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="C161" s="6" t="s">
-        <v>492</v>
+        <v>482</v>
       </c>
       <c r="D161" s="6" t="s">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="E161" s="6" t="s">
-        <v>418</v>
+        <v>408</v>
       </c>
       <c r="F161" s="6" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="G161" s="2">
         <v>1.6407111258729501</v>
@@ -11192,8 +11194,8 @@
   <sheetFormatPr defaultColWidth="70" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="4" width="70" style="1"/>
-    <col min="5" max="5" width="17.375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="92.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="92.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
@@ -11201,143 +11203,143 @@
         <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>493</v>
+        <v>483</v>
       </c>
     </row>
     <row r="2" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E2" s="4" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>494</v>
+        <v>484</v>
       </c>
     </row>
     <row r="3" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E3" s="2" t="s">
-        <v>1</v>
+        <v>512</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>495</v>
+        <v>485</v>
       </c>
     </row>
     <row r="4" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E4" s="2" t="s">
-        <v>2</v>
+        <v>514</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>496</v>
+        <v>486</v>
       </c>
     </row>
     <row r="5" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E5" s="2" t="s">
-        <v>3</v>
+        <v>515</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>497</v>
+        <v>487</v>
       </c>
     </row>
     <row r="6" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E6" s="2" t="s">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>498</v>
+        <v>488</v>
       </c>
     </row>
     <row r="7" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E7" s="2" t="s">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>499</v>
+        <v>489</v>
       </c>
     </row>
     <row r="8" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E8" s="2" t="s">
-        <v>6</v>
+        <v>501</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>500</v>
+        <v>490</v>
       </c>
     </row>
     <row r="9" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E9" s="2" t="s">
-        <v>509</v>
+        <v>502</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>511</v>
+        <v>497</v>
       </c>
     </row>
     <row r="10" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E10" s="2" t="s">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>512</v>
+        <v>498</v>
       </c>
     </row>
     <row r="11" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E11" s="2" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>515</v>
+        <v>499</v>
       </c>
     </row>
     <row r="12" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E12" s="2" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
     </row>
     <row r="13" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E13" s="2" t="s">
-        <v>7</v>
+        <v>509</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>502</v>
+        <v>491</v>
       </c>
     </row>
     <row r="14" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E14" s="2" t="s">
-        <v>8</v>
+        <v>506</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>503</v>
+        <v>492</v>
       </c>
     </row>
     <row r="15" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E15" s="2" t="s">
-        <v>9</v>
+        <v>510</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>504</v>
+        <v>493</v>
       </c>
     </row>
     <row r="16" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E16" s="2" t="s">
-        <v>10</v>
+        <v>507</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>505</v>
+        <v>494</v>
       </c>
     </row>
     <row r="17" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E17" s="2" t="s">
-        <v>11</v>
+        <v>511</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>506</v>
+        <v>495</v>
       </c>
     </row>
     <row r="18" spans="5:6" ht="14.25" x14ac:dyDescent="0.15">
       <c r="E18" s="2" t="s">
-        <v>12</v>
+        <v>508</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>507</v>
+        <v>496</v>
       </c>
     </row>
   </sheetData>
